--- a/backend/data/EventData.xlsx
+++ b/backend/data/EventData.xlsx
@@ -426,7 +426,7 @@
         <v>Foosball</v>
       </c>
       <c r="C2" t="str">
-        <v>/icons/foosball.svg</v>
+        <v>/Icons/foosball.svg</v>
       </c>
       <c r="D2" t="str">
         <v>Table soccer played with rods and miniature players, requiring quick reflexes and strategic play.</v>
@@ -440,7 +440,7 @@
         <v>Carrom</v>
       </c>
       <c r="C3" t="str">
-        <v>/icons/carrom.svg</v>
+        <v>/Icons/carrom.svg</v>
       </c>
       <c r="D3" t="str">
         <v>Fast-paced tabletop game where players flick discs into pockets, combining skill and strategy.</v>
@@ -454,7 +454,7 @@
         <v>Chess</v>
       </c>
       <c r="C4" t="str">
-        <v>/icons/chess.svg</v>
+        <v>/Icons/chess.svg</v>
       </c>
       <c r="D4" t="str">
         <v>Classic strategic board game of kings and queens, testing players' tactical thinking.</v>
@@ -468,7 +468,7 @@
         <v>Table Tennis</v>
       </c>
       <c r="C5" t="str">
-        <v>/icons/table-tennis.svg</v>
+        <v>/Icons/table-tennis.svg</v>
       </c>
       <c r="D5" t="str">
         <v>Fast-paced racket sport played on a table, demanding quick reflexes and precision.</v>
@@ -482,7 +482,7 @@
         <v>Badminton</v>
       </c>
       <c r="C6" t="str">
-        <v>/icons/badminton.svg</v>
+        <v>/Icons/badminton.svg</v>
       </c>
       <c r="D6" t="str">
         <v>High-energy racket sport played with a shuttlecock, requiring agility and tactical play.</v>
@@ -496,7 +496,7 @@
         <v>Cricket</v>
       </c>
       <c r="C7" t="str">
-        <v>/icons/cricket.svg</v>
+        <v>/Icons/cricket.svg</v>
       </c>
       <c r="D7" t="str">
         <v>Team sport played with bat and ball, combining individual skill with team strategy.</v>
@@ -510,7 +510,7 @@
         <v>Football</v>
       </c>
       <c r="C8" t="str">
-        <v>/icons/football.svg</v>
+        <v>/Icons/football.svg</v>
       </c>
       <c r="D8" t="str">
         <v>The beautiful game played between two teams of eleven players each.</v>
@@ -524,7 +524,7 @@
         <v>Basketball</v>
       </c>
       <c r="C9" t="str">
-        <v>/icons/basketball.svg</v>
+        <v>/Icons/basketball.svg</v>
       </c>
       <c r="D9" t="str">
         <v>Fast-paced team sport played with a ball and hoop, requiring coordination and teamwork.</v>
@@ -538,7 +538,7 @@
         <v>Lemon Spoon Race</v>
       </c>
       <c r="C10" t="str">
-        <v>/icons/lemon-spoon.svg</v>
+        <v>/Icons/lemon-spoon.svg</v>
       </c>
       <c r="D10" t="str">
         <v>Fun relay race where participants balance a lemon on a spoon while running.</v>

--- a/backend/data/EventData.xlsx
+++ b/backend/data/EventData.xlsx
@@ -976,7 +976,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:I8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1000,6 +1000,12 @@
       <c r="G1" t="str">
         <v>Status</v>
       </c>
+      <c r="H1" t="str">
+        <v>TeamA_ID</v>
+      </c>
+      <c r="I1" t="str">
+        <v>TeamB_ID</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -1139,9 +1145,38 @@
         <v>Scheduled</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Quarterfinal</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2025-06-23</v>
+      </c>
+      <c r="E8" t="str">
+        <v>12:12</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Recreation Area</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Scheduled</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I8"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/backend/data/EventData.xlsx
+++ b/backend/data/EventData.xlsx
@@ -976,7 +976,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:G7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1000,12 +1000,6 @@
       <c r="G1" t="str">
         <v>Status</v>
       </c>
-      <c r="H1" t="str">
-        <v>TeamA_ID</v>
-      </c>
-      <c r="I1" t="str">
-        <v>TeamB_ID</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -1145,38 +1139,9 @@
         <v>Scheduled</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>3</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Quarterfinal</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2025-06-23</v>
-      </c>
-      <c r="E8" t="str">
-        <v>12:12</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Recreation Area</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Scheduled</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
   </ignoredErrors>
 </worksheet>
 </file>
